--- a/survey_templates/044_crowdstrike_global_security_attitude_survey--survey_templates.xlsx
+++ b/survey_templates/044_crowdstrike_global_security_attitude_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'very_important',_'label':_'very_important'}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Very Important', 'label': 'Very Important'}</t>
+          <t>Very Important</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_important',_'label':_'somewhat_important'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Important', 'label': 'Somewhat Important'}</t>
+          <t>Somewhat Important</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'not_very_important',_'label':_'not_very_important'}</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Not Very Important', 'label': 'Not Very Important'}</t>
+          <t>Not Very Important</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'not_at_all_important',_'label':_'not_at_all_important'}</t>
+          <t>not_at_all_important</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Not at all Important', 'label': 'Not at all Important'}</t>
+          <t>Not at all Important</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'very_important',_'label':_'very_important'}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Very Important', 'label': 'Very Important'}</t>
+          <t>Very Important</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_important',_'label':_'somewhat_important'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Important', 'label': 'Somewhat Important'}</t>
+          <t>Somewhat Important</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'not_very_important',_'label':_'not_very_important'}</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Not Very Important', 'label': 'Not Very Important'}</t>
+          <t>Not Very Important</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'not_at_all_important',_'label':_'not_at_all_important'}</t>
+          <t>not_at_all_important</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Not at all Important', 'label': 'Not at all Important'}</t>
+          <t>Not at all Important</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'very_confident',_'label':_'very_confident'}</t>
+          <t>very_confident</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Very Confident', 'label': 'Very Confident'}</t>
+          <t>Very Confident</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_confident',_'label':_'somewhat_confident'}</t>
+          <t>somewhat_confident</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Confident', 'label': 'Somewhat Confident'}</t>
+          <t>Somewhat Confident</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'not_very_confident',_'label':_'not_very_confident'}</t>
+          <t>not_very_confident</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Not Very Confident', 'label': 'Not Very Confident'}</t>
+          <t>Not Very Confident</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'not_at_all_confident',_'label':_'not_at_all_confident'}</t>
+          <t>not_at_all_confident</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Not at all Confident', 'label': 'Not at all Confident'}</t>
+          <t>Not at all Confident</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'very_effective',_'label':_'very_effective'}</t>
+          <t>very_effective</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Very Effective', 'label': 'Very Effective'}</t>
+          <t>Very Effective</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_effective',_'label':_'somewhat_effective'}</t>
+          <t>somewhat_effective</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Effective', 'label': 'Somewhat Effective'}</t>
+          <t>Somewhat Effective</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'not_very_effective',_'label':_'not_very_effective'}</t>
+          <t>not_very_effective</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Not Very Effective', 'label': 'Not Very Effective'}</t>
+          <t>Not Very Effective</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'not_at_all_effective',_'label':_'not_at_all_effective'}</t>
+          <t>not_at_all_effective</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Not at all Effective', 'label': 'Not at all Effective'}</t>
+          <t>Not at all Effective</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'very_effective',_'label':_'very_effective'}</t>
+          <t>very_effective</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Very Effective', 'label': 'Very Effective'}</t>
+          <t>Very Effective</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_effective',_'label':_'somewhat_effective'}</t>
+          <t>somewhat_effective</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Effective', 'label': 'Somewhat Effective'}</t>
+          <t>Somewhat Effective</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'not_very_effective',_'label':_'not_very_effective'}</t>
+          <t>not_very_effective</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Not Very Effective', 'label': 'Not Very Effective'}</t>
+          <t>Not Very Effective</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'not_at_all_effective',_'label':_'not_at_all_effective'}</t>
+          <t>not_at_all_effective</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Not at all Effective', 'label': 'Not at all Effective'}</t>
+          <t>Not at all Effective</t>
         </is>
       </c>
     </row>
